--- a/DataTables/Datas/level.xlsx
+++ b/DataTables/Datas/level.xlsx
@@ -27,27 +27,36 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="30">
   <si>
     <t>##var</t>
   </si>
   <si>
-    <t>Id</t>
-  </si>
-  <si>
-    <t>Intro</t>
-  </si>
-  <si>
-    <t>Title</t>
-  </si>
-  <si>
-    <t>Time</t>
-  </si>
-  <si>
-    <t>TargetScore</t>
-  </si>
-  <si>
-    <t>ImagePath</t>
+    <t>id</t>
+  </si>
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>tip</t>
+  </si>
+  <si>
+    <t>time</t>
+  </si>
+  <si>
+    <t>target_score</t>
+  </si>
+  <si>
+    <t>image_path1</t>
+  </si>
+  <si>
+    <t>image_path2</t>
+  </si>
+  <si>
+    <t>image_path3</t>
+  </si>
+  <si>
+    <t>tip_infos</t>
   </si>
   <si>
     <t>##type</t>
@@ -59,6 +68,9 @@
     <t>string</t>
   </si>
   <si>
+    <t>(list#sep=|),string</t>
+  </si>
+  <si>
     <t>##group</t>
   </si>
   <si>
@@ -71,31 +83,40 @@
     <t>唯一字段</t>
   </si>
   <si>
-    <t>备注</t>
+    <t>标题</t>
   </si>
   <si>
     <t>描述</t>
   </si>
   <si>
-    <t>标题</t>
-  </si>
-  <si>
     <t>时间</t>
   </si>
   <si>
-    <t>分数</t>
+    <t>目标分数</t>
   </si>
   <si>
     <t>图片1</t>
   </si>
   <si>
-    <t>L01_Intro</t>
+    <t>图片2</t>
+  </si>
+  <si>
+    <t>图片3</t>
+  </si>
+  <si>
+    <t>提示列表</t>
   </si>
   <si>
     <t>L01_Title</t>
   </si>
   <si>
+    <t>L01_Tip</t>
+  </si>
+  <si>
     <t>L01_Image</t>
+  </si>
+  <si>
+    <t>DoorLock|Window|Curtain|Takeout|BedsidePhone|HandPhone|SocketWire|Footprint</t>
   </si>
 </sst>
 </file>
@@ -1288,8 +1309,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="7"/>
+  <dimension ref="A1:J5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4"/>
   <cols>
     <col min="4" max="4" width="20" customWidth="1"/>
     <col min="5" max="5" width="22.5" customWidth="1"/>
@@ -1297,122 +1318,155 @@
     <col min="8" max="8" width="24.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" spans="1:8">
+    <row r="1" ht="14.25" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1"/>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="2" ht="14.25" spans="1:8">
+    <row r="2" ht="14.25" spans="1:10">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="1"/>
+        <v>11</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="D2" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
+      </c>
+      <c r="I2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="3" ht="14.25" spans="1:8">
+    <row r="3" ht="14.25" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="1"/>
+        <v>15</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="D3" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
+      </c>
+      <c r="I3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="4" ht="14.25" spans="1:8">
+    <row r="4" ht="14.25" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
+      </c>
+      <c r="I4" t="s">
+        <v>24</v>
+      </c>
+      <c r="J4" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:10">
       <c r="B5">
         <v>1</v>
       </c>
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
       <c r="D5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" t="s">
-        <v>21</v>
+        <v>27</v>
+      </c>
+      <c r="E5">
+        <v>180</v>
       </c>
       <c r="F5">
-        <v>180</v>
-      </c>
-      <c r="G5">
-        <v>14</v>
-      </c>
-      <c r="H5" t="s">
-        <v>22</v>
+        <v>8</v>
+      </c>
+      <c r="G5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J5" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
